--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3633" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3633" uniqueCount="649">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -656,16 +656,6 @@
     <t>檢驗檢查分類</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Observation.category:VSCat.id</t>
   </si>
   <si>
@@ -938,6 +928,24 @@
     <t>https://twcore.mohw.gov.tw/ig/twcore/ValueSet/vital-signs-tw</t>
   </si>
   <si>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
+  </si>
+  <si>
     <t>Observation.code.id</t>
   </si>
   <si>
@@ -967,12 +975,6 @@
   </si>
   <si>
     <t>允許代碼系統中的替代編碼，以及翻譯到其他編碼系統。</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
   </si>
   <si>
     <t>Observation.code.coding.id</t>
@@ -1137,7 +1139,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1148,9 +1150,6 @@
   </si>
   <si>
     <t>通常檢驗檢查的對象是一位病人或一群病人、地點或設備，檢驗檢查對象與直接測量內容之間的區別在observation.code已具體說明（例如： 「血糖」），不需要使用這個資料項目（focus）單獨表示。如果需要參照檢體，則使用specimen，如果需要一個代碼而不是一個resource，則使用bodysite來表示bodysites或標準擴充focusCode。</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -1536,6 +1535,13 @@
     <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
+    <t>obs-6
+vs-2</t>
+  </si>
+  <si>
+    <t>value.nullFlavor</t>
+  </si>
+  <si>
     <t>Observation.interpretation</t>
   </si>
   <si>
@@ -1561,6 +1567,18 @@
     <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values|</t>
+  </si>
+  <si>
+    <t>OBX-8</t>
+  </si>
+  <si>
+    <t>interpretationCode</t>
+  </si>
+  <si>
+    <t>363713009 |Has interpretation|</t>
+  </si>
+  <si>
     <t>Observation.note</t>
   </si>
   <si>
@@ -1602,6 +1620,18 @@
     <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
+    <t>&lt; 123037004 |Body structure|</t>
+  </si>
+  <si>
+    <t>OBX-20</t>
+  </si>
+  <si>
+    <t>targetSiteCode</t>
+  </si>
+  <si>
+    <t>718497002 |Inherent location|</t>
+  </si>
+  <si>
     <t>Observation.method</t>
   </si>
   <si>
@@ -1618,6 +1648,12 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+  </si>
+  <si>
+    <t>OBX-17</t>
+  </si>
+  <si>
+    <t>methodCode</t>
   </si>
   <si>
     <t>Observation.specimen</t>
@@ -1652,7 +1688,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1733,7 +1769,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1783,6 +1819,18 @@
     <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
+    <t>&lt; 260245000 |Findings values| OR  +&lt; 365860008 |General clinical state finding| +OR +&lt; 250171008 |Clinical history or observation findings| OR  +&lt; 415229000 |Racial group| OR +&lt; 365400002 |Finding of puberty stage| OR+&lt; 443938003 |Procedure carried out on subject|</t>
+  </si>
+  <si>
+    <t>OBX-10</t>
+  </si>
+  <si>
     <t>Observation.referenceRange.appliesTo</t>
   </si>
   <si>
@@ -1925,6 +1973,10 @@
     <t>代碼指明檢驗檢查的名稱；可參考所綁定值集，但此值集只是針對這個欄位的一個可能值的範例，不預期也不鼓勵使用者一定要使用此值集的代碼。</t>
   </si>
   <si>
+    <t>&lt; 363787002 |Observable entity| OR +&lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1967,6 +2019,10 @@
   </si>
   <si>
     <t>代碼指明為什麼結果（Observation.value[x]）缺少；應填入所綁定值集中適合的代碼，確定無適合的代碼才可以使用其他值集的代碼來表示。</t>
+  </si>
+  <si>
+    <t>obs-6
+vs-3</t>
   </si>
   <si>
     <t>Observation.component.interpretation</t>
@@ -2340,7 +2396,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="46.26953125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.10546875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="91.75" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="31.65234375" customWidth="true" bestFit="true"/>
@@ -4257,7 +4313,7 @@
         <v>81</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
         <v>104</v>
@@ -4269,13 +4325,13 @@
         <v>20</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>206</v>
+        <v>20</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>20</v>
+        <v>201</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>20</v>
@@ -4283,10 +4339,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4309,13 +4365,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -4366,7 +4422,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -4390,7 +4446,7 @@
         <v>20</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>20</v>
@@ -4401,10 +4457,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4433,7 +4489,7 @@
         <v>140</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>142</v>
@@ -4474,10 +4530,10 @@
         <v>20</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>20</v>
@@ -4486,7 +4542,7 @@
         <v>199</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -4510,7 +4566,7 @@
         <v>20</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4521,10 +4577,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4547,19 +4603,19 @@
         <v>93</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>224</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>225</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4608,7 +4664,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4629,10 +4685,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4643,10 +4699,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4669,13 +4725,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4726,7 +4782,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -4750,7 +4806,7 @@
         <v>20</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>20</v>
@@ -4761,10 +4817,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4793,7 +4849,7 @@
         <v>140</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>142</v>
@@ -4834,10 +4890,10 @@
         <v>20</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>20</v>
@@ -4846,7 +4902,7 @@
         <v>199</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -4870,7 +4926,7 @@
         <v>20</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>20</v>
@@ -4881,10 +4937,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4910,23 +4966,23 @@
         <v>106</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O22" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>20</v>
@@ -4968,7 +5024,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -4989,10 +5045,10 @@
         <v>20</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AO22" t="s" s="2">
         <v>20</v>
@@ -5003,10 +5059,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5029,16 +5085,16 @@
         <v>93</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
@@ -5088,7 +5144,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -5109,10 +5165,10 @@
         <v>20</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>20</v>
@@ -5123,10 +5179,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5152,21 +5208,21 @@
         <v>112</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>20</v>
@@ -5208,7 +5264,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -5229,10 +5285,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -5243,10 +5299,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5269,17 +5325,17 @@
         <v>93</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -5328,7 +5384,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -5349,10 +5405,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -5363,10 +5419,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5389,19 +5445,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N26" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5450,7 +5506,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5471,10 +5527,10 @@
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO26" t="s" s="2">
         <v>20</v>
@@ -5485,10 +5541,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5511,19 +5567,19 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L27" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O27" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M27" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>20</v>
@@ -5572,7 +5628,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5593,10 +5649,10 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>20</v>
@@ -5607,14 +5663,14 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5630,22 +5686,22 @@
         <v>20</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>194</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5670,13 +5726,13 @@
         <v>20</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>20</v>
@@ -5694,7 +5750,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>92</v>
@@ -5703,36 +5759,36 @@
         <v>92</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>20</v>
+        <v>294</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>20</v>
+        <v>295</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP28" t="s" s="2">
-        <v>20</v>
+        <v>299</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5755,13 +5811,13 @@
         <v>20</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5812,7 +5868,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5836,7 +5892,7 @@
         <v>20</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO29" t="s" s="2">
         <v>20</v>
@@ -5847,10 +5903,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5876,10 +5932,10 @@
         <v>139</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -5918,10 +5974,10 @@
         <v>20</v>
       </c>
       <c r="AB30" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC30" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD30" t="s" s="2">
         <v>20</v>
@@ -5930,7 +5986,7 @@
         <v>199</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5965,10 +6021,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5988,22 +6044,22 @@
         <v>20</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>20</v>
@@ -6052,7 +6108,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -6061,7 +6117,7 @@
         <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ31" t="s" s="2">
         <v>104</v>
@@ -6073,10 +6129,10 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>307</v>
+        <v>226</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>308</v>
+        <v>227</v>
       </c>
       <c r="AO31" t="s" s="2">
         <v>20</v>
@@ -6087,10 +6143,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6113,13 +6169,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -6170,7 +6226,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -6194,7 +6250,7 @@
         <v>20</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>20</v>
@@ -6205,10 +6261,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6234,13 +6290,13 @@
         <v>139</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -6278,10 +6334,10 @@
         <v>20</v>
       </c>
       <c r="AB33" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC33" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD33" t="s" s="2">
         <v>20</v>
@@ -6290,7 +6346,7 @@
         <v>199</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -6325,10 +6381,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6354,16 +6410,16 @@
         <v>106</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O34" t="s" s="2">
         <v>237</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -6373,7 +6429,7 @@
         <v>20</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>20</v>
@@ -6412,7 +6468,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -6433,10 +6489,10 @@
         <v>20</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6447,10 +6503,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6473,16 +6529,16 @@
         <v>93</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -6532,7 +6588,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6553,10 +6609,10 @@
         <v>20</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
@@ -6567,10 +6623,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6596,14 +6652,14 @@
         <v>112</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6613,7 +6669,7 @@
         <v>20</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>20</v>
@@ -6652,7 +6708,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6673,10 +6729,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6687,10 +6743,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6713,17 +6769,17 @@
         <v>93</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6733,7 +6789,7 @@
         <v>20</v>
       </c>
       <c r="S37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="T37" t="s" s="2">
         <v>20</v>
@@ -6772,7 +6828,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6793,10 +6849,10 @@
         <v>20</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
@@ -6807,10 +6863,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6833,19 +6889,19 @@
         <v>93</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>269</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>275</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6894,7 +6950,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6915,10 +6971,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6929,10 +6985,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6955,19 +7011,19 @@
         <v>93</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>280</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="O39" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>284</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>20</v>
@@ -7016,7 +7072,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -7037,10 +7093,10 @@
         <v>20</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
@@ -7051,10 +7107,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7077,19 +7133,19 @@
         <v>93</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>20</v>
@@ -7138,7 +7194,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -7153,19 +7209,19 @@
         <v>104</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>20</v>
@@ -7173,10 +7229,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7199,13 +7255,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7256,7 +7312,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -7280,7 +7336,7 @@
         <v>20</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -7291,10 +7347,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7323,7 +7379,7 @@
         <v>140</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N42" t="s" s="2">
         <v>142</v>
@@ -7364,10 +7420,10 @@
         <v>20</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC42" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD42" t="s" s="2">
         <v>20</v>
@@ -7376,7 +7432,7 @@
         <v>199</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -7400,7 +7456,7 @@
         <v>20</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>20</v>
@@ -7411,10 +7467,10 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7437,16 +7493,16 @@
         <v>93</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7496,7 +7552,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -7505,7 +7561,7 @@
         <v>92</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>104</v>
@@ -7531,10 +7587,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7560,13 +7616,13 @@
         <v>106</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -7592,13 +7648,13 @@
         <v>20</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>20</v>
@@ -7616,7 +7672,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7651,10 +7707,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7680,13 +7736,13 @@
         <v>151</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7736,7 +7792,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7760,7 +7816,7 @@
         <v>20</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7771,10 +7827,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7797,16 +7853,16 @@
         <v>93</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7856,7 +7912,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7891,10 +7947,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7917,16 +7973,16 @@
         <v>93</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -7976,7 +8032,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7997,13 +8053,13 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>365</v>
+        <v>296</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>366</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>20</v>
@@ -8521,13 +8577,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8578,7 +8634,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8602,7 +8658,7 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8645,7 +8701,7 @@
         <v>140</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N53" t="s" s="2">
         <v>142</v>
@@ -8686,10 +8742,10 @@
         <v>20</v>
       </c>
       <c r="AB53" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC53" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD53" t="s" s="2">
         <v>20</v>
@@ -8698,7 +8754,7 @@
         <v>199</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8722,7 +8778,7 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8759,16 +8815,16 @@
         <v>93</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>411</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
@@ -8818,7 +8874,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -8827,7 +8883,7 @@
         <v>92</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>104</v>
@@ -8882,13 +8938,13 @@
         <v>106</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8914,13 +8970,13 @@
         <v>20</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>20</v>
@@ -8938,7 +8994,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -9002,13 +9058,13 @@
         <v>151</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9058,7 +9114,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9082,7 +9138,7 @@
         <v>20</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AO56" t="s" s="2">
         <v>20</v>
@@ -9119,16 +9175,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9178,7 +9234,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9276,7 +9332,7 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y58" t="s" s="2">
         <v>421</v>
@@ -9398,7 +9454,7 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y59" t="s" s="2">
         <v>421</v>
@@ -9483,13 +9539,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9540,7 +9596,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9564,7 +9620,7 @@
         <v>20</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
@@ -9607,7 +9663,7 @@
         <v>140</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>142</v>
@@ -9648,10 +9704,10 @@
         <v>20</v>
       </c>
       <c r="AB61" t="s" s="2">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="AC61" t="s" s="2">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="AD61" t="s" s="2">
         <v>20</v>
@@ -9660,7 +9716,7 @@
         <v>199</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9684,7 +9740,7 @@
         <v>20</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>
@@ -9965,7 +10021,7 @@
         <v>93</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L64" t="s" s="2">
         <v>459</v>
@@ -10364,7 +10420,7 @@
         <v>20</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y67" t="s" s="2">
         <v>487</v>
@@ -10397,7 +10453,7 @@
         <v>92</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>205</v>
+        <v>489</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>104</v>
@@ -10409,10 +10465,10 @@
         <v>20</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>207</v>
+        <v>490</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>20</v>
@@ -10423,14 +10479,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10452,16 +10508,16 @@
         <v>191</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>20</v>
@@ -10486,13 +10542,13 @@
         <v>20</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>20</v>
@@ -10510,7 +10566,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -10519,7 +10575,7 @@
         <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>104</v>
@@ -10528,27 +10584,27 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>206</v>
+        <v>500</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>207</v>
+        <v>501</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>20</v>
+        <v>502</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10571,19 +10627,19 @@
         <v>20</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>20</v>
@@ -10632,7 +10688,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10653,10 +10709,10 @@
         <v>20</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>20</v>
@@ -10667,10 +10723,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10696,13 +10752,13 @@
         <v>191</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10728,11 +10784,11 @@
         <v>20</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y70" s="2"/>
       <c r="Z70" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>20</v>
@@ -10750,7 +10806,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10759,7 +10815,7 @@
         <v>92</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>104</v>
@@ -10768,27 +10824,27 @@
         <v>20</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>20</v>
+        <v>516</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>206</v>
+        <v>517</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>207</v>
+        <v>518</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>20</v>
+        <v>519</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10814,16 +10870,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>511</v>
+        <v>521</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>512</v>
+        <v>522</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>513</v>
+        <v>523</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>514</v>
+        <v>524</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>20</v>
@@ -10848,11 +10904,11 @@
         <v>20</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>515</v>
+        <v>525</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>20</v>
@@ -10870,7 +10926,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>510</v>
+        <v>520</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10879,7 +10935,7 @@
         <v>92</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>104</v>
@@ -10891,10 +10947,10 @@
         <v>20</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>206</v>
+        <v>526</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>207</v>
+        <v>527</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>20</v>
@@ -10905,10 +10961,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10931,16 +10987,16 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>519</v>
+        <v>531</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -10990,7 +11046,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -11008,27 +11064,27 @@
         <v>20</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>524</v>
+        <v>536</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11051,16 +11107,16 @@
         <v>20</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>528</v>
+        <v>540</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11110,7 +11166,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11128,27 +11184,27 @@
         <v>20</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>533</v>
+        <v>545</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11171,19 +11227,19 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>20</v>
@@ -11232,7 +11288,7 @@
         <v>20</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11244,7 +11300,7 @@
         <v>20</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>20</v>
@@ -11253,10 +11309,10 @@
         <v>20</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>20</v>
@@ -11267,10 +11323,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11293,13 +11349,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11350,7 +11406,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -11374,7 +11430,7 @@
         <v>20</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>20</v>
@@ -11385,10 +11441,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>544</v>
+        <v>556</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11417,7 +11473,7 @@
         <v>140</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>142</v>
@@ -11470,7 +11526,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11494,7 +11550,7 @@
         <v>20</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>20</v>
@@ -11505,14 +11561,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11534,10 +11590,10 @@
         <v>139</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>142</v>
@@ -11592,7 +11648,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -11627,10 +11683,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11653,13 +11709,13 @@
         <v>20</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>552</v>
+        <v>564</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11710,7 +11766,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>80</v>
@@ -11719,7 +11775,7 @@
         <v>92</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>104</v>
@@ -11731,10 +11787,10 @@
         <v>20</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>20</v>
@@ -11745,10 +11801,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11771,13 +11827,13 @@
         <v>20</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11828,7 +11884,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11837,7 +11893,7 @@
         <v>92</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>104</v>
@@ -11849,10 +11905,10 @@
         <v>20</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>20</v>
@@ -11863,10 +11919,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11892,16 +11948,16 @@
         <v>191</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>20</v>
@@ -11929,10 +11985,10 @@
         <v>117</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11950,7 +12006,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>560</v>
+        <v>572</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -11959,7 +12015,7 @@
         <v>92</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>104</v>
@@ -11968,13 +12024,13 @@
         <v>20</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>20</v>
+        <v>579</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>206</v>
+        <v>580</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>207</v>
+        <v>501</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>20</v>
@@ -11985,10 +12041,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12014,16 +12070,16 @@
         <v>191</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>568</v>
+        <v>582</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>569</v>
+        <v>583</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>570</v>
+        <v>584</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>20</v>
@@ -12048,13 +12104,13 @@
         <v>20</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>571</v>
+        <v>585</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>572</v>
+        <v>586</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>573</v>
+        <v>587</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>20</v>
@@ -12072,7 +12128,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>567</v>
+        <v>581</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12081,7 +12137,7 @@
         <v>81</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ81" t="s" s="2">
         <v>104</v>
@@ -12090,13 +12146,13 @@
         <v>20</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>20</v>
+        <v>579</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>206</v>
+        <v>580</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>207</v>
+        <v>501</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>20</v>
@@ -12107,10 +12163,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12133,17 +12189,17 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>575</v>
+        <v>589</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>576</v>
+        <v>590</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>577</v>
+        <v>591</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>578</v>
+        <v>592</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>20</v>
@@ -12192,7 +12248,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>574</v>
+        <v>588</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -12216,7 +12272,7 @@
         <v>20</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>579</v>
+        <v>593</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>20</v>
@@ -12227,10 +12283,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12253,13 +12309,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>581</v>
+        <v>595</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>582</v>
+        <v>596</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12310,7 +12366,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>580</v>
+        <v>594</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12331,10 +12387,10 @@
         <v>20</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>583</v>
+        <v>597</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>20</v>
@@ -12345,10 +12401,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12371,16 +12427,16 @@
         <v>93</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>585</v>
+        <v>599</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>586</v>
+        <v>600</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>587</v>
+        <v>601</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>588</v>
+        <v>602</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12430,7 +12486,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>584</v>
+        <v>598</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -12451,10 +12507,10 @@
         <v>20</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>590</v>
+        <v>604</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>20</v>
@@ -12465,10 +12521,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12491,16 +12547,16 @@
         <v>93</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>592</v>
+        <v>606</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>593</v>
+        <v>607</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>594</v>
+        <v>608</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>595</v>
+        <v>609</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12550,7 +12606,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12571,10 +12627,10 @@
         <v>20</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>589</v>
+        <v>603</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>596</v>
+        <v>610</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>20</v>
@@ -12585,10 +12641,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12611,19 +12667,19 @@
         <v>93</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>598</v>
+        <v>612</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>599</v>
+        <v>613</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>600</v>
+        <v>614</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>601</v>
+        <v>615</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>20</v>
@@ -12672,7 +12728,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>597</v>
+        <v>611</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12684,7 +12740,7 @@
         <v>20</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>602</v>
+        <v>616</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>20</v>
@@ -12693,10 +12749,10 @@
         <v>20</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>603</v>
+        <v>617</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>604</v>
+        <v>618</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>20</v>
@@ -12707,10 +12763,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>605</v>
+        <v>619</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12733,13 +12789,13 @@
         <v>20</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12790,7 +12846,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12814,7 +12870,7 @@
         <v>20</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>20</v>
@@ -12825,10 +12881,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>606</v>
+        <v>620</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12857,7 +12913,7 @@
         <v>140</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>142</v>
@@ -12910,7 +12966,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -12934,7 +12990,7 @@
         <v>20</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>20</v>
@@ -12945,14 +13001,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>607</v>
+        <v>621</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12974,10 +13030,10 @@
         <v>139</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>142</v>
@@ -13032,7 +13088,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13067,10 +13123,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13090,22 +13146,22 @@
         <v>20</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K90" t="s" s="2">
         <v>191</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>609</v>
+        <v>623</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>610</v>
+        <v>624</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>611</v>
+        <v>625</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>20</v>
@@ -13130,13 +13186,13 @@
         <v>20</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>612</v>
+        <v>626</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>20</v>
@@ -13154,7 +13210,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>608</v>
+        <v>622</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>92</v>
@@ -13163,7 +13219,7 @@
         <v>92</v>
       </c>
       <c r="AI90" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ90" t="s" s="2">
         <v>104</v>
@@ -13172,16 +13228,16 @@
         <v>20</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>20</v>
+        <v>627</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>206</v>
+        <v>296</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>207</v>
+        <v>297</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>20</v>
+        <v>298</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>20</v>
@@ -13189,10 +13245,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13215,19 +13271,19 @@
         <v>93</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>614</v>
+        <v>629</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>615</v>
+        <v>630</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>616</v>
+        <v>631</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>617</v>
+        <v>632</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>618</v>
+        <v>633</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>20</v>
@@ -13252,13 +13308,13 @@
         <v>20</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>619</v>
+        <v>634</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>620</v>
+        <v>635</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>20</v>
@@ -13276,7 +13332,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>613</v>
+        <v>628</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13285,7 +13341,7 @@
         <v>92</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>621</v>
+        <v>636</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>104</v>
@@ -13294,7 +13350,7 @@
         <v>20</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>622</v>
+        <v>637</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>427</v>
@@ -13311,10 +13367,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13340,10 +13396,10 @@
         <v>191</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>624</v>
+        <v>639</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>625</v>
+        <v>640</v>
       </c>
       <c r="N92" t="s" s="2">
         <v>485</v>
@@ -13374,10 +13430,10 @@
         <v>20</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>626</v>
+        <v>641</v>
       </c>
       <c r="Z92" t="s" s="2">
         <v>488</v>
@@ -13398,7 +13454,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>623</v>
+        <v>638</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13407,7 +13463,7 @@
         <v>92</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>205</v>
+        <v>642</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>104</v>
@@ -13419,10 +13475,10 @@
         <v>20</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>206</v>
+        <v>136</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>207</v>
+        <v>490</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>20</v>
@@ -13433,14 +13489,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13462,16 +13518,16 @@
         <v>191</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>628</v>
+        <v>644</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>20</v>
@@ -13496,13 +13552,13 @@
         <v>20</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>629</v>
+        <v>645</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>20</v>
@@ -13520,7 +13576,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>627</v>
+        <v>643</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13529,7 +13585,7 @@
         <v>81</v>
       </c>
       <c r="AI93" t="s" s="2">
-        <v>205</v>
+        <v>20</v>
       </c>
       <c r="AJ93" t="s" s="2">
         <v>104</v>
@@ -13538,27 +13594,27 @@
         <v>20</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>20</v>
+        <v>499</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>206</v>
+        <v>500</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>207</v>
+        <v>501</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>20</v>
+        <v>502</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13584,16 +13640,16 @@
         <v>82</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>632</v>
+        <v>648</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>20</v>
@@ -13642,7 +13698,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>630</v>
+        <v>646</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13663,10 +13719,10 @@
         <v>20</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
+++ b/docs/StructureDefinition-PASportObservationPeripheralOxygenSaturation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
